--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39F76117-C83C-44C1-9A34-C89B075673ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C30302D-2D7A-48DF-A87A-6819D1F5B0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
+    <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
   <si>
     <t>After 2010</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Hyperion</t>
   </si>
   <si>
-    <t>NPack - Can compress 32bits and 64bits exe, dll, ocx, scr Windows program.</t>
-  </si>
-  <si>
     <t>PESpin</t>
   </si>
   <si>
@@ -71,51 +68,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>LIAPP - Easiest and most powerful mobile app security solution.</t>
-  </si>
-  <si>
-    <t>LM-X License Manager - LM-X License Manager lets you protect your products against piracy by enforcing various levels of security, save time, and reduce business risks.</t>
-  </si>
-  <si>
-    <t>m0dern_p4cker - Just a modern packer for elf binaries ( works on linux executables only ).</t>
-  </si>
-  <si>
-    <t>MidgetPack - Midgetpack is a binary packer for ELF binaries, such as burneye, upx or other tools.</t>
-  </si>
-  <si>
-    <t>MPRESS - Compresses (using LZMA) and protects PE, .NET or Mach-O programs against reverse engineering.</t>
-  </si>
-  <si>
-    <t>NetCrypt - A proof-of-concept packer for .NET executables, designed to provide a starting point to explain the basic principles of runtime packing.</t>
-  </si>
-  <si>
-    <t>.netshrink - Executable compressor for your Windows or Linux .NET application executable file using LZMA.</t>
-  </si>
-  <si>
-    <t>Obsidium - Feature-rich professional software protection and licensing system designed as a cost effective and easy to implement, yet reliable and non-invasive way to protect your 32- and 64-bit Windows software applications and games from reverse engineering.</t>
-  </si>
-  <si>
-    <t>Origami - Packer compressing .net assemblies, (ab)using the PE format for data storage.</t>
-  </si>
-  <si>
-    <t>OS-X_Packer - Binary packer for the Mach-O file format.</t>
-  </si>
-  <si>
-    <t>Pakkero - Pakkero is a binary packer written in Go made for fun and educational purpose.</t>
-  </si>
-  <si>
-    <t>Pakr - In-memory packer for macOS Mach-O bundles.</t>
-  </si>
-  <si>
-    <t>Papaw - Permissively-licensed packer for ELF executables using LZMA Zstandard or Deflate compression.</t>
-  </si>
-  <si>
-    <t>PE-Packer - Simple packer for Windows 32-bits PE files.</t>
-  </si>
-  <si>
-    <t>PE-Toy - A PE file packer.</t>
-  </si>
-  <si>
     <t>PELock - Software protection system for Windows executable files ; protects your applications from tampering and reverse engineering, and provides extensive support for software license key management, including support for time trial periods.</t>
   </si>
   <si>
@@ -161,27 +113,15 @@
     <t>Themida - From Renovo paper: Themida converts the original x86 instructions into virtual instructions in its own randomized instruction set, and then interpret these virtual instructions at run-time.</t>
   </si>
   <si>
-    <t>UPX - Ultimate Packer for eXecutables.</t>
-  </si>
-  <si>
     <t>VirtualMachineObfuscationPoC - Obfuscation method using virtual machine.</t>
   </si>
   <si>
     <t>VMProtect - VMProtect protects code by executing it on a virtual machine with non-standard architecture that makes it extremely difficult to analyze and crack the software.</t>
   </si>
   <si>
-    <t>Ward - Simple implementation of an ELF packer that creates stealthy droppers for loading malicious ELFs in-memory.</t>
-  </si>
-  <si>
-    <t>Woody Wood Packer - ELF packer - encrypt and inject self-decryption code into executable ELF binary target.</t>
-  </si>
-  <si>
     <t>xorPacker - Simple packer working with all PE files which cipher your exe with a XOR implementation.</t>
   </si>
   <si>
-    <t>zELF - A modular ELF64 packer for Linux x86_64 featuring 22 compression codecs, ML-based codec selection, and support for both static and PIE binaries.</t>
-  </si>
-  <si>
     <t>ZProtect - Renames metadata entities and supports advanced obfuscation methods that harden protection scheme and foil reverse engineering altogether.</t>
   </si>
   <si>
@@ -309,13 +249,79 @@
   </si>
   <si>
     <t>EXE Bundle</t>
+  </si>
+  <si>
+    <t>m0dern_p4cker</t>
+  </si>
+  <si>
+    <t>Papaw</t>
+  </si>
+  <si>
+    <t>MidgetPack</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Woody Wood Packer</t>
+  </si>
+  <si>
+    <t>zELF</t>
+  </si>
+  <si>
+    <t>NetCrypt</t>
+  </si>
+  <si>
+    <t>.netshrink</t>
+  </si>
+  <si>
+    <t>Pakr</t>
+  </si>
+  <si>
+    <t>UPX</t>
+  </si>
+  <si>
+    <t>LIAPP</t>
+  </si>
+  <si>
+    <t>Non Freeware</t>
+  </si>
+  <si>
+    <t>LM-X License Manager</t>
+  </si>
+  <si>
+    <t>MPRESS</t>
+  </si>
+  <si>
+    <t>NSPack.</t>
+  </si>
+  <si>
+    <t>Obsidium</t>
+  </si>
+  <si>
+    <t>Origami</t>
+  </si>
+  <si>
+    <t>OS-X_Packer</t>
+  </si>
+  <si>
+    <t>extra help</t>
+  </si>
+  <si>
+    <t>Pakkero</t>
+  </si>
+  <si>
+    <t>PE-Packer</t>
+  </si>
+  <si>
+    <t>PE-Toy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +382,12 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -398,7 +410,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -419,12 +431,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -864,1090 +877,1267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B8DFFA-58CB-400E-9827-ACD5D99E1F0E}">
   <dimension ref="A1:E184"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.4140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" style="2" customWidth="1"/>
     <col min="5" max="5" width="27" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="2"/>
+    <col min="6" max="16384" width="8.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="9">
+        <v>44713</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10">
-        <v>44713</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="9">
+        <v>29</v>
+      </c>
+      <c r="B4" s="8">
         <v>41395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="9">
+        <v>32</v>
+      </c>
+      <c r="B5" s="8">
         <v>43009</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="9">
+        <v>33</v>
+      </c>
+      <c r="B6" s="8">
         <v>40787</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="9">
+        <v>34</v>
+      </c>
+      <c r="B7" s="8">
         <v>41214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="11">
+        <v>38</v>
+      </c>
+      <c r="B8" s="10">
         <v>36175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2">
         <v>2021</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2">
         <v>1998</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2">
         <v>1999</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2">
         <v>1999</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2">
         <v>2023</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="9">
+        <v>44</v>
+      </c>
+      <c r="B14" s="8">
         <v>36161</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2">
         <v>2004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B16" s="2">
         <v>2010</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="9">
+        <v>47</v>
+      </c>
+      <c r="B17" s="8">
         <v>38869</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
         <v>2010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>39858</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2">
         <v>2006</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="10">
+        <v>41794</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="10">
+        <v>38554</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="11">
-        <v>41794</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="11">
-        <v>38554</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="B23" s="2">
         <v>2007</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2">
         <v>2012</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="B25" s="2">
         <v>2011</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="11">
+        <v>56</v>
+      </c>
+      <c r="B26" s="10">
         <v>41676</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2">
         <v>2017</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2">
         <v>2000</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2">
         <v>2018</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2">
         <v>2016</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2">
         <v>2014</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2">
         <v>2004</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="11">
+        <v>64</v>
+      </c>
+      <c r="B33" s="10">
         <v>40455</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B34" s="2">
         <v>2017</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B35" s="2">
         <v>2001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B36" s="2">
         <v>2002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2">
         <v>2018</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B38" s="2">
         <v>1992</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B39" s="2">
         <v>2012</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="C39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="2">
         <v>2011</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="52.5">
+      <c r="C40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="10">
+        <v>42780</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="10">
+        <v>43704</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="10">
+        <v>41844</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="10">
+        <v>39893</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="10">
+        <v>41562</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="10">
+        <v>43172</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="10">
+        <v>43920</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="10">
+        <v>36974</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="10">
+        <v>44903</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="10">
+        <v>42740</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" s="10">
+        <v>43848</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="227.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="140" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="140">
-      <c r="A42" s="6" t="s">
+    <row r="59" spans="1:5" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="87.5">
-      <c r="A43" s="6" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="105">
-      <c r="A44" s="6" t="s">
+    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="105">
-      <c r="A45" s="6" t="s">
+    <row r="63" spans="1:5" ht="35" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="140">
-      <c r="A46" s="6" t="s">
+    <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="105">
-      <c r="A47" s="6" t="s">
+    <row r="65" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="70">
-      <c r="A48" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="227.5">
-      <c r="A49" s="6" t="s">
+    <row r="66" spans="1:4" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="87.5">
-      <c r="A50" s="6" t="s">
+    <row r="67" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="52.5">
-      <c r="A51" s="6" t="s">
+    <row r="68" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="70">
-      <c r="A52" s="6" t="s">
+    <row r="69" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="52.5">
-      <c r="A53" s="6" t="s">
+    <row r="70" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="87.5">
-      <c r="A54" s="6" t="s">
+    <row r="71" spans="1:4" ht="35" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="52.5">
-      <c r="A55" s="6" t="s">
+    <row r="72" spans="1:4" ht="157.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="35">
-      <c r="A56" s="6" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="10">
+        <v>35941</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="227.5">
-      <c r="A57" s="6" t="s">
+    <row r="75" spans="1:4" ht="140" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="140">
-      <c r="A58" s="6" t="s">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="10">
+        <v>44042</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="10">
+        <v>44774</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="105">
-      <c r="A59" s="6" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" s="10">
+        <v>46002</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="105">
-      <c r="A61" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="122.5">
-      <c r="A62" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="35">
-      <c r="A63" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="122.5">
-      <c r="A64" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="87.5">
-      <c r="A65" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="70">
-      <c r="A66" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="70">
-      <c r="A67" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="105">
-      <c r="A68" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="140">
-      <c r="A69" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="105">
-      <c r="A70" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="35">
-      <c r="A71" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="192.5">
-      <c r="A72" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="35">
-      <c r="A73" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="70">
-      <c r="A74" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="140">
-      <c r="A75" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="105">
-      <c r="A76" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="105">
-      <c r="A77" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" ht="87.5">
-      <c r="A78" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" ht="140">
-      <c r="A79" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" ht="140">
-      <c r="A80" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" s="1"/>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
     </row>
   </sheetData>

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C30302D-2D7A-48DF-A87A-6819D1F5B0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140CCB7D-B167-4ACC-940A-0B39EE87B71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Old List" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="94">
   <si>
     <t>After 2010</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>PE-Toy</t>
+  </si>
+  <si>
+    <t>Not Building</t>
   </si>
 </sst>
 </file>
@@ -883,7 +886,7 @@
     <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" style="2" customWidth="1"/>
     <col min="6" max="16384" width="8.6328125" style="2"/>
   </cols>
   <sheetData>
@@ -1628,10 +1631,10 @@
         <v>44903</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -1666,10 +1669,28 @@
       <c r="A55" s="6" t="s">
         <v>91</v>
       </c>
+      <c r="B55" s="10">
+        <v>44179</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>92</v>
+      </c>
+      <c r="B56" s="10">
+        <v>42740</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="227.5" x14ac:dyDescent="0.35">

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140CCB7D-B167-4ACC-940A-0B39EE87B71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDF9F8B-2454-4AA9-84B1-D379989AA443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDF9F8B-2454-4AA9-84B1-D379989AA443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A61658-A9D7-4C4D-9F31-3ECF4B6C7379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
   <si>
     <t>After 2010</t>
   </si>
@@ -68,36 +68,12 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>PELock - Software protection system for Windows executable files ; protects your applications from tampering and reverse engineering, and provides extensive support for software license key management, including support for time trial periods.</t>
-  </si>
-  <si>
-    <t>PePacker - Simple PE Packer Which Encrypts .text Section I release a simple PE file packer which encrypts the .text section and adds a decryption stub to the end of the last section.</t>
-  </si>
-  <si>
-    <t>PEShield - PE-SHiELD is a program, which encrypts 32-bit Windows EXE files, leaving them still executable.</t>
-  </si>
-  <si>
-    <t>PEtite - Free Win32 (Windows 95/98/2000/NT/XP/Vista/7/etc) executable (EXE/DLL/etc) compressor.</t>
-  </si>
-  <si>
-    <t>PEzoNG - Framework for automatically creating stealth binaries that target a very low detection rate in a Windows environment.</t>
-  </si>
-  <si>
-    <t>PEzor - Open-Source Shellcode &amp; PE Packer.</t>
-  </si>
-  <si>
     <t>ProtectMyTooling - Multi-Packer wrapper letting us daisy-chain various packers, obfuscators and other Red Team oriented weaponry.</t>
   </si>
   <si>
     <t>RapidEXE - Simple and efficient way to convert a PHP/Python script to a standalone executable.</t>
   </si>
   <si>
-    <t>Silent-Packer - Silent Packer is an ELF / PE packer written in pure C.</t>
-  </si>
-  <si>
-    <t>Simple-PE32-Packer - Simple PE32 Packer with aPLib compression library.</t>
-  </si>
-  <si>
     <t>SimpleDPack - A very simple windows EXE packing tool for learning or investigating PE structure.</t>
   </si>
   <si>
@@ -107,15 +83,9 @@
     <t>Squishy - Modern packer developed for 64kb demoscene productions, targets 32bit and 64bit executables.</t>
   </si>
   <si>
-    <t>theArk - Windows x86 PE Packer In C++.</t>
-  </si>
-  <si>
     <t>Themida - From Renovo paper: Themida converts the original x86 instructions into virtual instructions in its own randomized instruction set, and then interpret these virtual instructions at run-time.</t>
   </si>
   <si>
-    <t>VirtualMachineObfuscationPoC - Obfuscation method using virtual machine.</t>
-  </si>
-  <si>
     <t>VMProtect - VMProtect protects code by executing it on a virtual machine with non-standard architecture that makes it extremely difficult to analyze and crack the software.</t>
   </si>
   <si>
@@ -317,7 +287,43 @@
     <t>PE-Toy</t>
   </si>
   <si>
-    <t>Not Building</t>
+    <t>Not Precompiled</t>
+  </si>
+  <si>
+    <t>PELock</t>
+  </si>
+  <si>
+    <t>PePacker</t>
+  </si>
+  <si>
+    <t>Pezor</t>
+  </si>
+  <si>
+    <t>Linux Packer</t>
+  </si>
+  <si>
+    <t>PEzoNG</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>PEShield</t>
+  </si>
+  <si>
+    <t>Petite</t>
+  </si>
+  <si>
+    <t>VirtualMachineObfuscationPoC</t>
+  </si>
+  <si>
+    <t>Simple-PE32-Packer</t>
+  </si>
+  <si>
+    <t>theArk</t>
+  </si>
+  <si>
+    <t>Silent-Packer</t>
   </si>
 </sst>
 </file>
@@ -882,7 +888,7 @@
   <dimension ref="A1:E184"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="37" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="2" customWidth="1"/>
@@ -912,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -923,7 +929,7 @@
         <v>44713</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -932,13 +938,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B4" s="8">
         <v>41395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -946,13 +952,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B5" s="8">
         <v>43009</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -960,61 +966,61 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B6" s="8">
         <v>40787</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B7" s="8">
         <v>41214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B8" s="10">
         <v>36175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2">
         <v>2021</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1022,13 +1028,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2">
         <v>1998</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -1036,13 +1042,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2">
         <v>1999</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -1050,27 +1056,27 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2">
         <v>1999</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2">
         <v>2023</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1078,55 +1084,55 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B14" s="8">
         <v>36161</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2">
         <v>2004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2">
         <v>2010</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B17" s="8">
         <v>38869</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>9</v>
@@ -1134,16 +1140,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2">
         <v>2010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1154,223 +1160,223 @@
         <v>39858</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2">
         <v>2006</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B21" s="10">
         <v>41794</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B22" s="10">
         <v>38554</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2">
         <v>2007</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2">
         <v>2012</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2">
         <v>2011</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B26" s="10">
         <v>41676</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2">
         <v>2017</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2">
         <v>2000</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2">
         <v>2018</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2">
         <v>2016</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2">
         <v>2014</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2">
         <v>2004</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B33" s="10">
         <v>40455</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2">
         <v>2017</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
@@ -1378,75 +1384,75 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B35" s="2">
         <v>2001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B36" s="2">
         <v>2002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B37" s="2">
         <v>2018</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2">
         <v>1992</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B39" s="2">
         <v>2012</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>9</v>
@@ -1460,7 +1466,7 @@
         <v>2011</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>9</v>
@@ -1468,212 +1474,212 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B41" s="10">
         <v>42780</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B42" s="2">
         <v>2010</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B43" s="10">
         <v>43704</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B44" s="10">
         <v>41844</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B45" s="10">
         <v>39893</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B46" s="10">
         <v>41562</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B47" s="2">
         <v>2001</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B48" s="10">
         <v>43172</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B49" s="10">
         <v>43920</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B50" s="2">
         <v>2021</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B51" s="10">
         <v>36974</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B52" s="10">
         <v>44903</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B53" s="10">
         <v>42740</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B54" s="10">
         <v>43848</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B55" s="10">
         <v>44179</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>9</v>
@@ -1681,172 +1687,271 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B56" s="10">
         <v>42740</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="227.5" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="140" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="B57" s="8">
+        <v>44256</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="87.5" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="B58" s="10">
+        <v>42882</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>12</v>
+        <v>90</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+      <c r="B60" s="2">
+        <v>1929</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+      <c r="B61" s="10">
+        <v>43776</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="35" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="B62" s="10">
+        <v>44458</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
-        <v>15</v>
+        <v>86</v>
+      </c>
+      <c r="B63" s="10">
+        <v>44034</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="70" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="52.5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="B66" s="10">
+        <v>43933</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>19</v>
+        <v>93</v>
+      </c>
+      <c r="B67" s="10">
+        <v>43283</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="35" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
-        <v>23</v>
+        <v>94</v>
+      </c>
+      <c r="B71" s="10">
+        <v>43786</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="157.5" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B73" s="10">
         <v>35941</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="B74" s="10">
+        <v>44476</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="140" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B76" s="10">
         <v>44042</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B77" s="10">
         <v>44774</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B79" s="10">
         <v>46002</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A61658-A9D7-4C4D-9F31-3ECF4B6C7379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BD3111-5D50-4E25-905C-C3855D3A1A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
+    <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
   <sheets>
-    <sheet name="Old List" sheetId="1" r:id="rId1"/>
+    <sheet name="2010s" sheetId="1" r:id="rId1"/>
+    <sheet name="Between 2000 and 2010" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="98">
   <si>
     <t>After 2010</t>
   </si>
@@ -68,33 +69,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>ProtectMyTooling - Multi-Packer wrapper letting us daisy-chain various packers, obfuscators and other Red Team oriented weaponry.</t>
-  </si>
-  <si>
-    <t>RapidEXE - Simple and efficient way to convert a PHP/Python script to a standalone executable.</t>
-  </si>
-  <si>
-    <t>SimpleDPack - A very simple windows EXE packing tool for learning or investigating PE structure.</t>
-  </si>
-  <si>
-    <t>Smart Packer - Packs 32 &amp; 64bit applications with DLLs, data files, 3rd party run-time into one single executable that runs instantly, with no installs or hassles.</t>
-  </si>
-  <si>
-    <t>Squishy - Modern packer developed for 64kb demoscene productions, targets 32bit and 64bit executables.</t>
-  </si>
-  <si>
-    <t>Themida - From Renovo paper: Themida converts the original x86 instructions into virtual instructions in its own randomized instruction set, and then interpret these virtual instructions at run-time.</t>
-  </si>
-  <si>
-    <t>VMProtect - VMProtect protects code by executing it on a virtual machine with non-standard architecture that makes it extremely difficult to analyze and crack the software.</t>
-  </si>
-  <si>
-    <t>xorPacker - Simple packer working with all PE files which cipher your exe with a XOR implementation.</t>
-  </si>
-  <si>
-    <t>ZProtect - Renames metadata entities and supports advanced obfuscation methods that harden protection scheme and foil reverse engineering altogether.</t>
-  </si>
-  <si>
     <t>Alternate EXE Packer</t>
   </si>
   <si>
@@ -119,9 +93,6 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Malware Packer Fix Later</t>
-  </si>
-  <si>
     <t>Armadillo</t>
   </si>
   <si>
@@ -324,6 +295,42 @@
   </si>
   <si>
     <t>Silent-Packer</t>
+  </si>
+  <si>
+    <t>RapidEXE</t>
+  </si>
+  <si>
+    <t>Themida</t>
+  </si>
+  <si>
+    <t>ProtectMyTooling</t>
+  </si>
+  <si>
+    <t>Wrapper</t>
+  </si>
+  <si>
+    <t>Smart Packer</t>
+  </si>
+  <si>
+    <t>SimpleDPack</t>
+  </si>
+  <si>
+    <t>Not Avaliable</t>
+  </si>
+  <si>
+    <t>VMProtect</t>
+  </si>
+  <si>
+    <t>Squishy</t>
+  </si>
+  <si>
+    <t>xorPacker</t>
+  </si>
+  <si>
+    <t>Educational Toy Packer</t>
+  </si>
+  <si>
+    <t>Zprotect</t>
   </si>
 </sst>
 </file>
@@ -891,7 +898,7 @@
     <col min="1" max="1" width="37" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.90625" style="2" customWidth="1"/>
     <col min="5" max="5" width="34.1796875" style="2" customWidth="1"/>
     <col min="6" max="16384" width="8.6328125" style="2"/>
   </cols>
@@ -918,7 +925,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -929,7 +936,7 @@
         <v>44713</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -938,13 +945,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8">
         <v>41395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -952,13 +959,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" s="8">
         <v>43009</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -966,61 +973,58 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>40787</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>41214</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10">
         <v>36175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>2021</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1028,13 +1032,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
         <v>1998</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -1042,13 +1046,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>1999</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -1056,27 +1060,27 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>1999</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>2023</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1084,55 +1088,55 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8">
         <v>36161</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
         <v>2004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
         <v>2010</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B17" s="8">
         <v>38869</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>9</v>
@@ -1140,16 +1144,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2">
         <v>2010</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1160,223 +1164,223 @@
         <v>39858</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2">
         <v>2006</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B21" s="10">
         <v>41794</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B22" s="10">
         <v>38554</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B23" s="2">
         <v>2007</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2">
         <v>2012</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2">
         <v>2011</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B26" s="10">
         <v>41676</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2">
         <v>2017</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2">
         <v>2000</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
         <v>2018</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
         <v>2016</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2">
         <v>2014</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B32" s="2">
         <v>2004</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B33" s="10">
         <v>40455</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B34" s="2">
         <v>2017</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
@@ -1384,75 +1388,75 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2">
         <v>2001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2">
         <v>2002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B37" s="2">
         <v>2018</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B38" s="2">
         <v>1992</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B39" s="2">
         <v>2012</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>9</v>
@@ -1466,7 +1470,7 @@
         <v>2011</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>9</v>
@@ -1474,212 +1478,212 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B41" s="10">
         <v>42780</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B42" s="2">
         <v>2010</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B43" s="10">
         <v>43704</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B44" s="10">
         <v>41844</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B45" s="10">
         <v>39893</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B46" s="10">
         <v>41562</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2">
         <v>2001</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B48" s="10">
         <v>43172</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B49" s="10">
         <v>43920</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B50" s="2">
         <v>2021</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B51" s="10">
         <v>36974</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B52" s="10">
         <v>44903</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B53" s="10">
         <v>42740</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B54" s="10">
         <v>43848</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B55" s="10">
         <v>44179</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>9</v>
@@ -1687,27 +1691,27 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B56" s="10">
         <v>42740</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B57" s="8">
         <v>44256</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
@@ -1715,30 +1719,30 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B58" s="10">
         <v>42882</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B59" s="2">
         <v>1998</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -1749,21 +1753,21 @@
         <v>1929</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B61" s="10">
         <v>43776</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
@@ -1771,187 +1775,268 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B62" s="10">
         <v>44458</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B63" s="10">
         <v>44034</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="105" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="70" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="B64" s="10">
+        <v>43587</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
-        <v>11</v>
+        <v>86</v>
+      </c>
+      <c r="B65" s="10">
+        <v>43587</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B66" s="10">
         <v>43933</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B67" s="10">
         <v>43283</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+      <c r="B68" s="10">
+        <v>44943</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="B69" s="8">
+        <v>41426</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
-        <v>14</v>
+        <v>94</v>
+      </c>
+      <c r="B70" s="10">
+        <v>44278</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B71" s="10">
         <v>43786</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="157.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
-        <v>15</v>
+        <v>87</v>
+      </c>
+      <c r="B72" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B73" s="10">
         <v>35941</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B74" s="10">
         <v>44476</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="140" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B76" s="10">
         <v>44042</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B77" s="10">
         <v>44774</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>17</v>
+        <v>95</v>
+      </c>
+      <c r="B78" s="10">
+        <v>44051</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B79" s="10">
         <v>46002</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="122.5" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
-        <v>18</v>
+        <v>97</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
@@ -2274,4 +2359,13 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B11A9B-35AB-45E7-BC8E-2CD5857D81DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BD3111-5D50-4E25-905C-C3855D3A1A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFFEB62-6C47-4939-ABB3-408FC259F4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="142">
   <si>
     <t>After 2010</t>
   </si>
@@ -331,13 +331,145 @@
   </si>
   <si>
     <t>Zprotect</t>
+  </si>
+  <si>
+    <t>EXECryptor - Protects EXE programs from reverse engineering, analysis, modifications and cracking.</t>
+  </si>
+  <si>
+    <t>ExeFog - Simple Win32 PE files packer.</t>
+  </si>
+  <si>
+    <t>eXPressor - Used as a compressor this tool can compress EXE files to half their normal size.</t>
+  </si>
+  <si>
+    <t>FSG - Fast Small Good, perfect compressor for small exes, eg.</t>
+  </si>
+  <si>
+    <t>GHF Protector - Executable packer / protector based on open source engines Morphine and AHPack.</t>
+  </si>
+  <si>
+    <t>HackStop - EXE and COM programs encrypter and protector.</t>
+  </si>
+  <si>
+    <t>Kkrunchy - Kkrunchy is a small exe packer primarily meant for 64k intros.</t>
+  </si>
+  <si>
+    <t>mPack - mPack - mario PACKersimple Win32 PE Executable compressor.</t>
+  </si>
+  <si>
+    <t>NSPack - 32/64-bits exe, dll, ocx, scr Windows program compressor.</t>
+  </si>
+  <si>
+    <t>NTPacker - PE file packer relying on aPlib for compression and/or XOR for encryption.</t>
+  </si>
+  <si>
+    <t>PECompact - Windows executable compressor featuring third-party plug-ins offering protection against reverse engineering.</t>
+  </si>
+  <si>
+    <t>RDMC - DMC algorithm based packer.</t>
+  </si>
+  <si>
+    <t>RLPack - Compresses your executables and dynamic link libraries in a way that keeps them small and has no effect on compressed file functionality.</t>
+  </si>
+  <si>
+    <t>Sentinel HASP Envelope - Wrapping application that protects the target application with a secure shield, providing a means to counteract reverse engineering and other anti-debugging measures.</t>
+  </si>
+  <si>
+    <t>sePACKER - Simple Executable Packer is compressing executables' code section inorder to decrease size of binary files.</t>
+  </si>
+  <si>
+    <t>tElock - Telock is a practical tool that intends to help developers who want to protect their work and reduce the size of the executable files.</t>
+  </si>
+  <si>
+    <t>TTProtect - Professional protection tool designed for software developers to protect their PE applications against illegal modification or decompilation.</t>
+  </si>
+  <si>
+    <t>UPX-Scrambler - Scrambler for files packed with UPX (up to 1.06) so that they cannot be unpacked with the '-d' option.</t>
+  </si>
+  <si>
+    <t>x86.Virtualizer - x86 Virtualizer.</t>
+  </si>
+  <si>
+    <t>XComp - PE32 image file packer and rebuilder.</t>
+  </si>
+  <si>
+    <t>Yoda Protector</t>
+  </si>
+  <si>
+    <t>Yoda Crypter</t>
+  </si>
+  <si>
+    <t>UPack </t>
+  </si>
+  <si>
+    <t>20to4</t>
+  </si>
+  <si>
+    <t>BurnEye</t>
+  </si>
+  <si>
+    <t>Shiva</t>
+  </si>
+  <si>
+    <t>WinUpack</t>
+  </si>
+  <si>
+    <t>Upack UI</t>
+  </si>
+  <si>
+    <t>Laturi</t>
+  </si>
+  <si>
+    <t>Exe32Pack</t>
+  </si>
+  <si>
+    <t>AHPack </t>
+  </si>
+  <si>
+    <t>ByteBoozer</t>
+  </si>
+  <si>
+    <t>RSCC</t>
+  </si>
+  <si>
+    <t>RUCC</t>
+  </si>
+  <si>
+    <t>AverCryptor</t>
+  </si>
+  <si>
+    <t>ACProtect</t>
+  </si>
+  <si>
+    <t>Application Protector</t>
+  </si>
+  <si>
+    <t>unstable build</t>
+  </si>
+  <si>
+    <t>not avaliable</t>
+  </si>
+  <si>
+    <t>Password Protector</t>
+  </si>
+  <si>
+    <t>EXE Guarder</t>
+  </si>
+  <si>
+    <t>EXE Wrapper</t>
+  </si>
+  <si>
+    <t>CryptExec</t>
+  </si>
+  <si>
+    <t>AT4RE Protector</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,6 +536,13 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -426,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -454,6 +593,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2363,9 +2503,336 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B11A9B-35AB-45E7-BC8E-2CD5857D81DF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="218.90625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFFEB62-6C47-4939-ABB3-408FC259F4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4C7662-6307-4937-B1F7-93F9EA476CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abanisenioluwa_oroj1\PycharmProjects\corpus\manifest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkoro\projects\automated-packing\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4C7662-6307-4937-B1F7-93F9EA476CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A054DE46-8213-4D6A-9DE3-B3029DBDC21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76690" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
   <sheets>
     <sheet name="2010s" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="147">
   <si>
     <t>After 2010</t>
   </si>
@@ -333,51 +333,6 @@
     <t>Zprotect</t>
   </si>
   <si>
-    <t>EXECryptor - Protects EXE programs from reverse engineering, analysis, modifications and cracking.</t>
-  </si>
-  <si>
-    <t>ExeFog - Simple Win32 PE files packer.</t>
-  </si>
-  <si>
-    <t>eXPressor - Used as a compressor this tool can compress EXE files to half their normal size.</t>
-  </si>
-  <si>
-    <t>FSG - Fast Small Good, perfect compressor for small exes, eg.</t>
-  </si>
-  <si>
-    <t>GHF Protector - Executable packer / protector based on open source engines Morphine and AHPack.</t>
-  </si>
-  <si>
-    <t>HackStop - EXE and COM programs encrypter and protector.</t>
-  </si>
-  <si>
-    <t>Kkrunchy - Kkrunchy is a small exe packer primarily meant for 64k intros.</t>
-  </si>
-  <si>
-    <t>mPack - mPack - mario PACKersimple Win32 PE Executable compressor.</t>
-  </si>
-  <si>
-    <t>NSPack - 32/64-bits exe, dll, ocx, scr Windows program compressor.</t>
-  </si>
-  <si>
-    <t>NTPacker - PE file packer relying on aPlib for compression and/or XOR for encryption.</t>
-  </si>
-  <si>
-    <t>PECompact - Windows executable compressor featuring third-party plug-ins offering protection against reverse engineering.</t>
-  </si>
-  <si>
-    <t>RDMC - DMC algorithm based packer.</t>
-  </si>
-  <si>
-    <t>RLPack - Compresses your executables and dynamic link libraries in a way that keeps them small and has no effect on compressed file functionality.</t>
-  </si>
-  <si>
-    <t>Sentinel HASP Envelope - Wrapping application that protects the target application with a secure shield, providing a means to counteract reverse engineering and other anti-debugging measures.</t>
-  </si>
-  <si>
-    <t>sePACKER - Simple Executable Packer is compressing executables' code section inorder to decrease size of binary files.</t>
-  </si>
-  <si>
     <t>tElock - Telock is a practical tool that intends to help developers who want to protect their work and reduce the size of the executable files.</t>
   </si>
   <si>
@@ -463,13 +418,73 @@
   </si>
   <si>
     <t>AT4RE Protector</t>
+  </si>
+  <si>
+    <t>Segement Fault on Win11</t>
+  </si>
+  <si>
+    <t>EXECryptor</t>
+  </si>
+  <si>
+    <t>ExeFog</t>
+  </si>
+  <si>
+    <t>Non Compiled</t>
+  </si>
+  <si>
+    <t>GHF Protector</t>
+  </si>
+  <si>
+    <t>NSPack</t>
+  </si>
+  <si>
+    <t>sePACKER</t>
+  </si>
+  <si>
+    <t>Compatibility Issues Windows 11</t>
+  </si>
+  <si>
+    <t>eXPressor</t>
+  </si>
+  <si>
+    <t>FSG</t>
+  </si>
+  <si>
+    <t>Kkrunchy</t>
+  </si>
+  <si>
+    <t>HackStop</t>
+  </si>
+  <si>
+    <t>mPack</t>
+  </si>
+  <si>
+    <t>Non PE-32 output</t>
+  </si>
+  <si>
+    <t>NTPacker</t>
+  </si>
+  <si>
+    <t>PECompact</t>
+  </si>
+  <si>
+    <t>RLPack</t>
+  </si>
+  <si>
+    <t>Sentinel HASP Envelope</t>
+  </si>
+  <si>
+    <t>Enterprise Product</t>
+  </si>
+  <si>
+    <t>RDMC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,10 +605,10 @@
     <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1033,25 +1048,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B8DFFA-58CB-400E-9827-ACD5D99E1F0E}">
   <dimension ref="A1:E184"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="37" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.90625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.1796875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.6328125" style="2"/>
+    <col min="2" max="2" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.8984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.19921875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.59765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1068,7 +1083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1083,7 +1098,7 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1097,7 +1112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
@@ -1125,7 +1140,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
@@ -1139,7 +1154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1156,7 +1171,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -1170,7 +1185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -1184,7 +1199,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -1198,7 +1213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1212,7 +1227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
@@ -1226,7 +1241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
@@ -1240,7 +1255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
         <v>25</v>
       </c>
@@ -1254,7 +1269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
         <v>26</v>
       </c>
@@ -1268,7 +1283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
@@ -1296,7 +1311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
         <v>1</v>
       </c>
@@ -1313,7 +1328,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
@@ -1327,7 +1342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
@@ -1341,7 +1356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
@@ -1355,7 +1370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
@@ -1369,7 +1384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
@@ -1383,7 +1398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
         <v>35</v>
       </c>
@@ -1397,7 +1412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
         <v>36</v>
       </c>
@@ -1411,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
@@ -1425,7 +1440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
         <v>41</v>
       </c>
@@ -1442,7 +1457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
@@ -1456,7 +1471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
@@ -1470,7 +1485,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
         <v>40</v>
       </c>
@@ -1484,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
@@ -1498,7 +1513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
         <v>44</v>
       </c>
@@ -1512,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
@@ -1526,7 +1541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
         <v>50</v>
       </c>
@@ -1543,7 +1558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
         <v>48</v>
       </c>
@@ -1560,7 +1575,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
         <v>47</v>
       </c>
@@ -1574,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
         <v>46</v>
       </c>
@@ -1588,7 +1603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
         <v>49</v>
       </c>
@@ -1602,7 +1617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
         <v>2</v>
       </c>
@@ -1616,7 +1631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
         <v>61</v>
       </c>
@@ -1630,7 +1645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="19.5" customHeight="1">
       <c r="A42" s="6" t="s">
         <v>63</v>
       </c>
@@ -1644,7 +1659,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
         <v>51</v>
       </c>
@@ -1658,7 +1673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
         <v>53</v>
       </c>
@@ -1672,7 +1687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
         <v>64</v>
       </c>
@@ -1686,7 +1701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
         <v>57</v>
       </c>
@@ -1700,7 +1715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
         <v>58</v>
       </c>
@@ -1714,7 +1729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
         <v>65</v>
       </c>
@@ -1728,7 +1743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
         <v>66</v>
       </c>
@@ -1745,7 +1760,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
         <v>67</v>
       </c>
@@ -1759,7 +1774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
         <v>68</v>
       </c>
@@ -1773,7 +1788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
         <v>70</v>
       </c>
@@ -1787,7 +1802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
         <v>59</v>
       </c>
@@ -1801,7 +1816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
         <v>52</v>
       </c>
@@ -1815,7 +1830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
         <v>71</v>
       </c>
@@ -1829,7 +1844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
         <v>72</v>
       </c>
@@ -1843,7 +1858,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
         <v>74</v>
       </c>
@@ -1857,7 +1872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
         <v>75</v>
       </c>
@@ -1871,7 +1886,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
         <v>80</v>
       </c>
@@ -1885,7 +1900,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
         <v>3</v>
       </c>
@@ -1899,7 +1914,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
         <v>81</v>
       </c>
@@ -1913,7 +1928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
         <v>78</v>
       </c>
@@ -1927,7 +1942,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
         <v>76</v>
       </c>
@@ -1941,7 +1956,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
         <v>88</v>
       </c>
@@ -1955,7 +1970,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4">
       <c r="A65" s="6" t="s">
         <v>86</v>
       </c>
@@ -1969,7 +1984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4">
       <c r="A66" s="6" t="s">
         <v>85</v>
       </c>
@@ -1983,7 +1998,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4">
       <c r="A67" s="6" t="s">
         <v>83</v>
       </c>
@@ -1997,7 +2012,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4">
       <c r="A68" s="6" t="s">
         <v>91</v>
       </c>
@@ -2011,7 +2026,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4">
       <c r="A69" s="6" t="s">
         <v>90</v>
       </c>
@@ -2025,7 +2040,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4">
       <c r="A70" s="6" t="s">
         <v>94</v>
       </c>
@@ -2039,7 +2054,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4">
       <c r="A71" s="6" t="s">
         <v>84</v>
       </c>
@@ -2053,7 +2068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4">
       <c r="A72" s="6" t="s">
         <v>87</v>
       </c>
@@ -2067,7 +2082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4">
       <c r="A73" s="6" t="s">
         <v>60</v>
       </c>
@@ -2081,7 +2096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="22.05" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>82</v>
       </c>
@@ -2095,7 +2110,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4">
       <c r="A75" s="6" t="s">
         <v>93</v>
       </c>
@@ -2109,7 +2124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4">
       <c r="A76" s="6" t="s">
         <v>54</v>
       </c>
@@ -2123,7 +2138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4">
       <c r="A77" s="6" t="s">
         <v>55</v>
       </c>
@@ -2137,7 +2152,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4">
       <c r="A78" s="6" t="s">
         <v>95</v>
       </c>
@@ -2151,7 +2166,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4">
       <c r="A79" s="6" t="s">
         <v>56</v>
       </c>
@@ -2165,7 +2180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4">
       <c r="A80" s="6" t="s">
         <v>97</v>
       </c>
@@ -2179,316 +2194,316 @@
         <v>92</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1">
       <c r="A82" s="1"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1">
       <c r="A104" s="3"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1">
       <c r="A105" s="3"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1">
       <c r="A106" s="3"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1">
       <c r="A107" s="3"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1">
       <c r="A108" s="3"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1">
       <c r="A109" s="3"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1">
       <c r="A111" s="3"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1">
       <c r="A112" s="3"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1">
       <c r="A113" s="3"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1">
       <c r="A114" s="3"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1">
       <c r="A116" s="3"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1">
       <c r="A124" s="1"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1">
       <c r="A144" s="3"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1">
       <c r="A145" s="3"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1">
       <c r="A160" s="3"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1">
       <c r="A161" s="3"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1">
       <c r="A176" s="3"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1">
       <c r="A177" s="4"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1">
       <c r="A179" s="3"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1">
       <c r="A180" s="3"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1">
       <c r="A181" s="3"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1">
       <c r="A182" s="3"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1">
       <c r="A183" s="3"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1">
       <c r="A184" s="3"/>
     </row>
   </sheetData>
@@ -2504,15 +2519,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B11A9B-35AB-45E7-BC8E-2CD5857D81DF}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="218.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.7265625" style="13"/>
+    <col min="1" max="1" width="198.19921875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="12"/>
+    <col min="3" max="3" width="35.296875" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="8.69921875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
-        <v>121</v>
+    <row r="1" spans="1:3">
+      <c r="A1" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>12</v>
@@ -2521,9 +2538,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
-        <v>133</v>
+    <row r="2" spans="1:3">
+      <c r="A2" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>11</v>
@@ -2532,9 +2549,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
-        <v>128</v>
+    <row r="3" spans="1:3">
+      <c r="A3" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>12</v>
@@ -2543,31 +2560,31 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
-        <v>134</v>
+    <row r="4" spans="1:3">
+      <c r="A4" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
-        <v>132</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -2576,64 +2593,64 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="13" t="s">
-        <v>139</v>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="13" t="s">
-        <v>127</v>
+      <c r="C11" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>11</v>
@@ -2642,138 +2659,222 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="12" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="13" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="12" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="13" t="s">
-        <v>120</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
@@ -2782,40 +2883,40 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="13" t="s">
-        <v>118</v>
+    <row r="35" spans="1:3">
+      <c r="A35" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
@@ -2824,7 +2925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3">
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkoro\projects\automated-packing\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A054DE46-8213-4D6A-9DE3-B3029DBDC21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5CE4CF-E7D5-4046-8C54-424884D9D857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="147">
   <si>
     <t>After 2010</t>
   </si>
@@ -333,21 +333,6 @@
     <t>Zprotect</t>
   </si>
   <si>
-    <t>tElock - Telock is a practical tool that intends to help developers who want to protect their work and reduce the size of the executable files.</t>
-  </si>
-  <si>
-    <t>TTProtect - Professional protection tool designed for software developers to protect their PE applications against illegal modification or decompilation.</t>
-  </si>
-  <si>
-    <t>UPX-Scrambler - Scrambler for files packed with UPX (up to 1.06) so that they cannot be unpacked with the '-d' option.</t>
-  </si>
-  <si>
-    <t>x86.Virtualizer - x86 Virtualizer.</t>
-  </si>
-  <si>
-    <t>XComp - PE32 image file packer and rebuilder.</t>
-  </si>
-  <si>
     <t>Yoda Protector</t>
   </si>
   <si>
@@ -478,6 +463,21 @@
   </si>
   <si>
     <t>RDMC</t>
+  </si>
+  <si>
+    <t>tElock</t>
+  </si>
+  <si>
+    <t>TTProtect</t>
+  </si>
+  <si>
+    <t>UPX-Scrambler</t>
+  </si>
+  <si>
+    <t>Xcomp</t>
+  </si>
+  <si>
+    <t>x86.Virtualizer</t>
   </si>
 </sst>
 </file>
@@ -2521,7 +2521,7 @@
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="198.19921875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="29.3984375" style="12" customWidth="1"/>
     <col min="2" max="2" width="8.69921875" style="12"/>
     <col min="3" max="3" width="35.296875" style="12" customWidth="1"/>
     <col min="4" max="16384" width="8.69921875" style="12"/>
@@ -2529,7 +2529,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>12</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>11</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>12</v>
@@ -2562,29 +2562,29 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>12</v>
@@ -2628,29 +2628,29 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="12" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>11</v>
@@ -2661,40 +2661,40 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="12" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>11</v>
@@ -2705,23 +2705,23 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>11</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -2743,18 +2743,18 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>12</v>
@@ -2765,7 +2765,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>12</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>11</v>
@@ -2787,18 +2787,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="12" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>11</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="12" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -2831,29 +2831,29 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="12" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
@@ -2864,17 +2864,29 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="12" t="s">
-        <v>98</v>
+        <v>142</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="12" t="s">
-        <v>99</v>
+        <v>143</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
@@ -2885,38 +2897,59 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="12" t="s">
-        <v>100</v>
+        <v>144</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="12" t="s">
-        <v>101</v>
+        <v>146</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="12" t="s">
-        <v>102</v>
+        <v>145</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>

--- a/manifest/packer_catalog.xlsx
+++ b/manifest/packer_catalog.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkoro\projects\automated-packing\corpus\manifest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5CE4CF-E7D5-4046-8C54-424884D9D857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9FF78D-9084-40CF-8F5A-8077DAE2593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="1" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
+    <workbookView xWindow="22944" yWindow="0" windowWidth="23232" windowHeight="25296" activeTab="2" xr2:uid="{0CDCCFCD-DE7E-40A9-A9AC-CA0E78A46E99}"/>
   </bookViews>
   <sheets>
     <sheet name="2010s" sheetId="1" r:id="rId1"/>
     <sheet name="Between 2000 and 2010" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="205">
   <si>
     <t>After 2010</t>
   </si>
@@ -438,9 +439,6 @@
     <t>Kkrunchy</t>
   </si>
   <si>
-    <t>HackStop</t>
-  </si>
-  <si>
     <t>mPack</t>
   </si>
   <si>
@@ -478,6 +476,183 @@
   </si>
   <si>
     <t>x86.Virtualizer</t>
+  </si>
+  <si>
+    <t>Fire-Pack</t>
+  </si>
+  <si>
+    <t>Pack-Ice</t>
+  </si>
+  <si>
+    <t>SPack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XPack </t>
+  </si>
+  <si>
+    <t>ABK Scrambler</t>
+  </si>
+  <si>
+    <t>AEP</t>
+  </si>
+  <si>
+    <t>AINEXE</t>
+  </si>
+  <si>
+    <t>aPack</t>
+  </si>
+  <si>
+    <t>AVPack</t>
+  </si>
+  <si>
+    <t>AXE</t>
+  </si>
+  <si>
+    <t>BIN-Lock</t>
+  </si>
+  <si>
+    <t>BitLok</t>
+  </si>
+  <si>
+    <t>C0NtRiVER</t>
+  </si>
+  <si>
+    <t>CauseWay Compressor</t>
+  </si>
+  <si>
+    <t>CC Pro</t>
+  </si>
+  <si>
+    <t>COMProtector</t>
+  </si>
+  <si>
+    <t>CrackStop</t>
+  </si>
+  <si>
+    <t>Crunch</t>
+  </si>
+  <si>
+    <t>Epack</t>
+  </si>
+  <si>
+    <t>ExeGuard</t>
+  </si>
+  <si>
+    <t>EXELOCK</t>
+  </si>
+  <si>
+    <t>FSE</t>
+  </si>
+  <si>
+    <t>Gardian Angel</t>
+  </si>
+  <si>
+    <t>JMCryptExe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGLZ </t>
+  </si>
+  <si>
+    <t>LzExe</t>
+  </si>
+  <si>
+    <t>Mask.</t>
+  </si>
+  <si>
+    <t>Megalit</t>
+  </si>
+  <si>
+    <t>Mess</t>
+  </si>
+  <si>
+    <t>Morphine.</t>
+  </si>
+  <si>
+    <t>Pro-Pack</t>
+  </si>
+  <si>
+    <t>RERP</t>
+  </si>
+  <si>
+    <t>RJCrush</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>$PIRIT</t>
+  </si>
+  <si>
+    <t>T-Pack</t>
+  </si>
+  <si>
+    <t>TinyProg</t>
+  </si>
+  <si>
+    <t>TRAP</t>
+  </si>
+  <si>
+    <t>Vacuum</t>
+  </si>
+  <si>
+    <t>VGCrypt</t>
+  </si>
+  <si>
+    <t>WinLite</t>
+  </si>
+  <si>
+    <t>XPA</t>
+  </si>
+  <si>
+    <t>XORER</t>
+  </si>
+  <si>
+    <t>XorCopy</t>
+  </si>
+  <si>
+    <t>WWPack</t>
+  </si>
+  <si>
+    <t>PEBundl</t>
+  </si>
+  <si>
+    <t>XE</t>
+  </si>
+  <si>
+    <t>CEXE</t>
+  </si>
+  <si>
+    <t>Neolite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACK </t>
+  </si>
+  <si>
+    <t>PCShrink</t>
+  </si>
+  <si>
+    <t>PE Diminisher</t>
+  </si>
+  <si>
+    <t>PE-Protector</t>
+  </si>
+  <si>
+    <t>PEPack</t>
+  </si>
+  <si>
+    <t>Pklite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shrinker </t>
+  </si>
+  <si>
+    <t>SysPack</t>
+  </si>
+  <si>
+    <t>SecuPack</t>
+  </si>
+  <si>
+    <t>32Lite</t>
   </si>
 </sst>
 </file>
@@ -580,7 +755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -608,6 +783,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2518,7 +2699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B11A9B-35AB-45E7-BC8E-2CD5857D81DF}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="29.3984375" style="12" customWidth="1"/>
@@ -2716,45 +2897,51 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="12" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="12" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>12</v>
@@ -2768,48 +2955,48 @@
         <v>136</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>129</v>
+        <v>137</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="12" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -2820,75 +3007,75 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>138</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>125</v>
+        <v>103</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="12" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
+      <c r="B32" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>129</v>
+        <v>100</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2897,26 +3084,29 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="12" t="s">
-        <v>144</v>
+        <v>104</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>105</v>
+        <v>145</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
@@ -2927,7 +3117,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="12" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
@@ -2938,7 +3128,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
@@ -2948,25 +3138,688 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B00558E-8614-4221-8952-D81C7C1D2BAB}">
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18">
+      <c r="A1" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18">
+      <c r="A2" s="14">
+        <v>624</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18">
+      <c r="A3" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18">
+      <c r="A4" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18">
+      <c r="A5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18">
+      <c r="A6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18">
+      <c r="A7" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18">
+      <c r="A8" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18">
+      <c r="A9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18">
+      <c r="A10" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18">
+      <c r="A11" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18">
+      <c r="A12" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18">
+      <c r="A13" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18">
+      <c r="A14" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18">
+      <c r="A15" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18">
+      <c r="A16" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18">
+      <c r="A17" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18">
+      <c r="A18" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18">
+      <c r="A19" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18">
+      <c r="A20" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18">
+      <c r="A21" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18">
+      <c r="A22" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18">
+      <c r="A23" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18">
+      <c r="A24" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18">
+      <c r="A25" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18">
+      <c r="A26" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18">
+      <c r="A27" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18">
+      <c r="A28" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18">
+      <c r="A29" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18">
+      <c r="A30" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18">
+      <c r="A31" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18">
+      <c r="A32" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18">
+      <c r="A33" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18">
+      <c r="A34" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18">
+      <c r="A35" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18">
+      <c r="A36" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18">
+      <c r="A37" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18">
+      <c r="A38" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18">
+      <c r="A39" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18">
+      <c r="A40" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18">
+      <c r="A41" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18">
+      <c r="A42" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18">
+      <c r="A43" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18">
+      <c r="A44" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="18">
+      <c r="A45" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18">
+      <c r="A46" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18">
+      <c r="A47" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18">
+      <c r="A48" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18">
+      <c r="A49" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18">
+      <c r="A50" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18">
+      <c r="A51" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18">
+      <c r="A52" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18">
+      <c r="A53" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18">
+      <c r="A54" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18">
+      <c r="A55" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18">
+      <c r="A56" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18">
+      <c r="A57" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18">
+      <c r="A58" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18">
+      <c r="A59" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18">
+      <c r="A60" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>